--- a/data/trans_dic/P64D$andando_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Clase-trans_dic.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,1; 33,65</t>
+          <t>23,2; 33,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>27,88; 36,69</t>
+          <t>28,11; 36,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,65; 33,46</t>
+          <t>26,72; 33,72</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,36; 25,82</t>
+          <t>16,3; 26,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,91; 36,75</t>
+          <t>26,22; 36,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,2; 29,0</t>
+          <t>21,83; 29,1</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,26; 25,48</t>
+          <t>3,17; 26,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,87; 56,78</t>
+          <t>38,23; 58,5</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 31,17</t>
+          <t>6,57; 30,97</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,98; 27,17</t>
+          <t>18,89; 26,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,26; 43,7</t>
+          <t>35,44; 44,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,47; 33,52</t>
+          <t>27,44; 33,38</t>
         </is>
       </c>
     </row>
@@ -772,24 +772,24 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,97; 18,75</t>
+          <t>8,86; 19,57</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>15,82; 38,46</t>
+          <t>14,72; 38,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 27,36</t>
+          <t>14,86; 27,16</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>33,98%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>25,67%</t>
         </is>
       </c>
     </row>
@@ -822,84 +822,33 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>12,73; 22,97</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>28,42; 37,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>19,05; 28,49</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>25,67%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="n"/>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>13,37; 23,03</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>28,71; 37,16</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>19,74; 28,61</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="A12:A13"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A16:A17"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A10:A11"/>
     <mergeCell ref="A14:A15"/>
@@ -914,7 +863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -927,7 +876,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando</t>
+          <t>Población que, al menos, se desplaza desde su casa al centro de trabajo/estudios andando (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1032,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81030; 118055</t>
+          <t>81397; 116834</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87155; 114684</t>
+          <t>87868; 115298</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>176810; 221952</t>
+          <t>177238; 223685</t>
         </is>
       </c>
     </row>
@@ -1105,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49638; 78325</t>
+          <t>49451; 78937</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>67842; 92656</t>
+          <t>66110; 92056</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>123335; 161113</t>
+          <t>121251; 161660</t>
         </is>
       </c>
     </row>
@@ -1178,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15962; 124726</t>
+          <t>15514; 127395</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27726; 41571</t>
+          <t>27992; 42826</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26408; 175418</t>
+          <t>36992; 174278</t>
         </is>
       </c>
     </row>
@@ -1251,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>106209; 152072</t>
+          <t>105704; 149850</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>150378; 186360</t>
+          <t>151149; 188077</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>270861; 330532</t>
+          <t>270614; 329187</t>
         </is>
       </c>
     </row>
@@ -1324,24 +1273,24 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21523; 44995</t>
+          <t>21257; 46945</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>59088; 143614</t>
+          <t>54962; 143426</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>93604; 167798</t>
+          <t>91144; 166592</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1351,17 +1300,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>395</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>761</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1156</t>
         </is>
       </c>
     </row>
@@ -1374,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>379431</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>488513</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>867943</t>
         </is>
       </c>
     </row>
@@ -1397,109 +1346,35 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>247296; 446322</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>408689; 534341</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>644187; 963194</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>n</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>395</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>761</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1156</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n"/>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>N (estimada)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>379431</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>488513</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>867943</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n"/>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>259911; 447460</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>412823; 534231</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>667343; 967434</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="A7:A9"/>
     <mergeCell ref="A4:A6"/>
     <mergeCell ref="A16:A18"/>
     <mergeCell ref="A10:A12"/>
     <mergeCell ref="A19:A21"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/trans_dic/P64D$andando_2023-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P64D$andando_2023-Clase-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29,98%</t>
+          <t>29,59%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>23,2; 33,3</t>
+          <t>22,35; 32,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>28,11; 36,88</t>
+          <t>27,69; 36,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 33,72</t>
+          <t>26,48; 33,24</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>25,41%</t>
+          <t>25,75%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>16,3; 26,02</t>
+          <t>16,8; 25,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,22; 36,51</t>
+          <t>26,24; 36,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21,83; 29,1</t>
+          <t>22,47; 29,23</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>47,7%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3,17; 26,02</t>
+          <t>19,59; 30,97</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38,23; 58,5</t>
+          <t>37,67; 57,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,57; 30,97</t>
+          <t>24,98; 34,77</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39,65%</t>
+          <t>40,16%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>31,21%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,89; 26,77</t>
+          <t>20,49; 28,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>35,44; 44,1</t>
+          <t>36,45; 44,51</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,44; 33,38</t>
+          <t>28,47; 34,12</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>26,18%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,86; 19,57</t>
+          <t>10,13; 20,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>14,72; 38,41</t>
+          <t>33,13; 42,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14,86; 27,16</t>
+          <t>22,62; 30,17</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>22,84%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>12,73; 22,97</t>
+          <t>20,97; 25,14</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,42; 37,16</t>
+          <t>34,41; 38,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,05; 28,49</t>
+          <t>27,39; 30,47</t>
         </is>
       </c>
     </row>
@@ -958,17 +958,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>98094</t>
+          <t>104538</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>100783</t>
+          <t>106967</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>198877</t>
+          <t>211505</t>
         </is>
       </c>
     </row>
@@ -981,17 +981,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81397; 116834</t>
+          <t>85321; 122908</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87868; 115298</t>
+          <t>92220; 121571</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>177238; 223685</t>
+          <t>189255; 237581</t>
         </is>
       </c>
     </row>
@@ -1031,17 +1031,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>62053</t>
+          <t>67214</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>79107</t>
+          <t>85848</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>141160</t>
+          <t>153062</t>
         </is>
       </c>
     </row>
@@ -1054,17 +1054,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49451; 78937</t>
+          <t>53888; 83072</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66110; 92056</t>
+          <t>71756; 100020</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121251; 161660</t>
+          <t>133557; 173726</t>
         </is>
       </c>
     </row>
@@ -1104,17 +1104,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>59183</t>
+          <t>67339</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>34926</t>
+          <t>39148</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94109</t>
+          <t>106487</t>
         </is>
       </c>
     </row>
@@ -1127,17 +1127,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>15514; 127395</t>
+          <t>53178; 84045</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27992; 42826</t>
+          <t>31258; 47776</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36992; 174278</t>
+          <t>88518; 123223</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>128522</t>
+          <t>150954</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>169099</t>
+          <t>192188</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>297621</t>
+          <t>343141</t>
         </is>
       </c>
     </row>
@@ -1200,17 +1200,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>105704; 149850</t>
+          <t>127166; 174453</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>151149; 188077</t>
+          <t>174463; 213020</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>270614; 329187</t>
+          <t>313000; 375099</t>
         </is>
       </c>
     </row>
@@ -1250,17 +1250,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>31579</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>104598</t>
+          <t>118098</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>136176</t>
+          <t>162304</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21257; 46945</t>
+          <t>31088; 62170</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>54962; 143426</t>
+          <t>103677; 133935</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>91144; 166592</t>
+          <t>140214; 186990</t>
         </is>
       </c>
     </row>
@@ -1323,17 +1323,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>379431</t>
+          <t>434250</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>488513</t>
+          <t>542249</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>867943</t>
+          <t>976499</t>
         </is>
       </c>
     </row>
@@ -1346,17 +1346,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>247296; 446322</t>
+          <t>398662; 478018</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>408689; 534341</t>
+          <t>509690; 575207</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>644187; 963194</t>
+          <t>926350; 1030733</t>
         </is>
       </c>
     </row>
